--- a/Оценки за период.xlsx
+++ b/Оценки за период.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ushkov\Desktop\school\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401FA02D-818E-4C96-8518-B46033D7F5E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="30">
   <si>
     <t>Учебный год: 2025/2026</t>
   </si>
@@ -20,7 +28,7 @@
     <t>Класс: 4О</t>
   </si>
   <si>
-    <t xml:space="preserve">Период:  c 12.01.2026 по 20.03.2026</t>
+    <t>Период:  c 12.01.2026 по 20.03.2026</t>
   </si>
   <si>
     <t>Ученик: Ушков Андрей Вячеславович</t>
@@ -107,9 +115,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -129,7 +136,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD3D3D3" tint="0"/>
+        <fgColor rgb="FFD3D3D3"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,188 +149,454 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+  <a:themeElements>
+    <a:clrScheme name="Стандартная">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Стандартная">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Стандартная">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:BB21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" customWidth="1"/>
-    <col min="20" max="20" width="9.140625" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" customWidth="1"/>
-    <col min="24" max="24" width="9.140625" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" customWidth="1"/>
-    <col min="27" max="27" width="9.140625" customWidth="1"/>
-    <col min="28" max="28" width="9.140625" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" customWidth="1"/>
-    <col min="30" max="30" width="9.140625" customWidth="1"/>
-    <col min="31" max="31" width="9.140625" customWidth="1"/>
-    <col min="32" max="32" width="9.140625" customWidth="1"/>
-    <col min="33" max="33" width="9.140625" customWidth="1"/>
-    <col min="34" max="34" width="9.140625" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" customWidth="1"/>
-    <col min="36" max="36" width="9.140625" customWidth="1"/>
-    <col min="37" max="37" width="9.140625" customWidth="1"/>
-    <col min="38" max="38" width="9.140625" customWidth="1"/>
-    <col min="39" max="39" width="9.140625" customWidth="1"/>
-    <col min="40" max="40" width="9.140625" customWidth="1"/>
-    <col min="41" max="41" width="9.140625" customWidth="1"/>
-    <col min="42" max="42" width="9.140625" customWidth="1"/>
-    <col min="43" max="43" width="9.140625" customWidth="1"/>
-    <col min="44" max="44" width="9.140625" customWidth="1"/>
-    <col min="45" max="45" width="9.140625" customWidth="1"/>
-    <col min="46" max="46" width="9.140625" customWidth="1"/>
-    <col min="47" max="47" width="9.140625" customWidth="1"/>
-    <col min="48" max="48" width="9.140625" customWidth="1"/>
-    <col min="49" max="49" width="9.140625" customWidth="1"/>
-    <col min="50" max="50" width="9.140625" customWidth="1"/>
-    <col min="51" max="51" width="9.140625" customWidth="1"/>
+    <col min="2" max="51" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="1"/>
-      <c r="AI8" s="1"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="1" t="s">
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AH8" s="4"/>
+      <c r="AI8" s="4"/>
+      <c r="AJ8" s="4"/>
+      <c r="AK8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AL8" s="1"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="1"/>
-      <c r="AO8" s="1"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="1"/>
-      <c r="AR8" s="1"/>
-      <c r="AS8" s="1"/>
-      <c r="AT8" s="1"/>
-      <c r="AU8" s="1"/>
-      <c r="AV8" s="1"/>
-      <c r="AW8" s="1"/>
-      <c r="AX8" s="1"/>
-      <c r="AY8" s="1"/>
-      <c r="AZ8" s="4" t="s">
+      <c r="AL8" s="4"/>
+      <c r="AM8" s="4"/>
+      <c r="AN8" s="4"/>
+      <c r="AO8" s="4"/>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="4"/>
+      <c r="AR8" s="4"/>
+      <c r="AS8" s="4"/>
+      <c r="AT8" s="4"/>
+      <c r="AU8" s="4"/>
+      <c r="AV8" s="4"/>
+      <c r="AW8" s="4"/>
+      <c r="AX8" s="4"/>
+      <c r="AY8" s="4"/>
+      <c r="AZ8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="BA8" s="4" t="s">
+      <c r="BA8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="BB8" s="4" t="s">
+      <c r="BB8" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="1"/>
+    <row r="9" spans="1:54" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
       <c r="B9" s="1">
         <v>12</v>
       </c>
@@ -474,11 +747,11 @@
       <c r="AY9" s="1">
         <v>20</v>
       </c>
-      <c r="AZ9" s="1"/>
-      <c r="BA9" s="1"/>
-      <c r="BB9" s="1"/>
+      <c r="AZ9" s="4"/>
+      <c r="BA9" s="4"/>
+      <c r="BB9" s="4"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -558,7 +831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -642,7 +915,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -727,7 +1000,7 @@
       <c r="AX12" s="3"/>
       <c r="AY12" s="3"/>
       <c r="AZ12" s="3">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="BA12" s="3">
         <v>4.71</v>
@@ -736,7 +1009,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -820,13 +1093,13 @@
         <v>4.7</v>
       </c>
       <c r="BA13" s="3">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="BB13" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
@@ -898,7 +1171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -974,7 +1247,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1046,7 +1319,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1383,7 @@
       </c>
       <c r="BB17" s="3"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
@@ -1146,8 +1419,8 @@
       <c r="S18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>21</v>
+      <c r="T18" s="3">
+        <v>5</v>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3" t="s">
@@ -1218,7 +1491,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1300,7 +1573,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
@@ -1386,7 +1659,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
@@ -1449,15 +1722,15 @@
       <c r="BB21" s="3"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="7">
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:P8"/>
     <mergeCell ref="Q8:AJ8"/>
     <mergeCell ref="AK8:AY8"/>
     <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
   </mergeCells>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Оценки за период.xlsx
+++ b/Оценки за период.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ushkov\Desktop\school\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401FA02D-818E-4C96-8518-B46033D7F5E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -115,7 +109,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -179,10 +173,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,14 +484,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:BB21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -526,77 +520,77 @@
       </c>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4" t="s">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
-      <c r="AF8" s="4"/>
-      <c r="AG8" s="4"/>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="4"/>
-      <c r="AJ8" s="4"/>
-      <c r="AK8" s="4" t="s">
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="5"/>
+      <c r="AJ8" s="5"/>
+      <c r="AK8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AL8" s="4"/>
-      <c r="AM8" s="4"/>
-      <c r="AN8" s="4"/>
-      <c r="AO8" s="4"/>
-      <c r="AP8" s="4"/>
-      <c r="AQ8" s="4"/>
-      <c r="AR8" s="4"/>
-      <c r="AS8" s="4"/>
-      <c r="AT8" s="4"/>
-      <c r="AU8" s="4"/>
-      <c r="AV8" s="4"/>
-      <c r="AW8" s="4"/>
-      <c r="AX8" s="4"/>
-      <c r="AY8" s="4"/>
-      <c r="AZ8" s="5" t="s">
+      <c r="AL8" s="5"/>
+      <c r="AM8" s="5"/>
+      <c r="AN8" s="5"/>
+      <c r="AO8" s="5"/>
+      <c r="AP8" s="5"/>
+      <c r="AQ8" s="5"/>
+      <c r="AR8" s="5"/>
+      <c r="AS8" s="5"/>
+      <c r="AT8" s="5"/>
+      <c r="AU8" s="5"/>
+      <c r="AV8" s="5"/>
+      <c r="AW8" s="5"/>
+      <c r="AX8" s="5"/>
+      <c r="AY8" s="5"/>
+      <c r="AZ8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="BA8" s="5" t="s">
+      <c r="BA8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="BB8" s="5" t="s">
+      <c r="BB8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:54" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="1">
         <v>12</v>
       </c>
@@ -747,9 +741,9 @@
       <c r="AY9" s="1">
         <v>20</v>
       </c>
-      <c r="AZ9" s="4"/>
-      <c r="BA9" s="4"/>
-      <c r="BB9" s="4"/>
+      <c r="AZ9" s="5"/>
+      <c r="BA9" s="5"/>
+      <c r="BB9" s="5"/>
     </row>
     <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -889,7 +883,9 @@
       </c>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
+      <c r="AL11" s="3">
+        <v>2</v>
+      </c>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>

--- a/Оценки за период.xlsx
+++ b/Оценки за период.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ushkov\Desktop\school\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9029A8-683C-4684-A1D5-C530C1D5530E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="30">
   <si>
     <t>Учебный год: 2025/2026</t>
   </si>
@@ -109,7 +115,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -161,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -178,6 +184,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -484,14 +494,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:BB21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -517,6 +527,12 @@
     <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="O7" s="7">
+        <f>SUM(B18:P18)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.25">
@@ -1383,31 +1399,31 @@
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6">
+        <v>5</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="3">
+        <v>4</v>
+      </c>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6" t="s">
         <v>13</v>
       </c>
       <c r="Q18" s="3"/>
@@ -1728,5 +1744,6 @@
     <mergeCell ref="AZ8:AZ9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Оценки за период.xlsx
+++ b/Оценки за период.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ushkov\Desktop\school\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9029A8-683C-4684-A1D5-C530C1D5530E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD3F72E-6DFF-478D-81A3-38694D6DF522}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -178,16 +178,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -530,83 +530,83 @@
       </c>
     </row>
     <row r="7" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="O7" s="7">
-        <f>SUM(B18:P18)</f>
+      <c r="O7" s="5">
+        <f>SUM(B18:O18)</f>
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="5"/>
-      <c r="AD8" s="5"/>
-      <c r="AE8" s="5"/>
-      <c r="AF8" s="5"/>
-      <c r="AG8" s="5"/>
-      <c r="AH8" s="5"/>
-      <c r="AI8" s="5"/>
-      <c r="AJ8" s="5"/>
-      <c r="AK8" s="5" t="s">
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="7"/>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AL8" s="5"/>
-      <c r="AM8" s="5"/>
-      <c r="AN8" s="5"/>
-      <c r="AO8" s="5"/>
-      <c r="AP8" s="5"/>
-      <c r="AQ8" s="5"/>
-      <c r="AR8" s="5"/>
-      <c r="AS8" s="5"/>
-      <c r="AT8" s="5"/>
-      <c r="AU8" s="5"/>
-      <c r="AV8" s="5"/>
-      <c r="AW8" s="5"/>
-      <c r="AX8" s="5"/>
-      <c r="AY8" s="5"/>
-      <c r="AZ8" s="4" t="s">
+      <c r="AL8" s="7"/>
+      <c r="AM8" s="7"/>
+      <c r="AN8" s="7"/>
+      <c r="AO8" s="7"/>
+      <c r="AP8" s="7"/>
+      <c r="AQ8" s="7"/>
+      <c r="AR8" s="7"/>
+      <c r="AS8" s="7"/>
+      <c r="AT8" s="7"/>
+      <c r="AU8" s="7"/>
+      <c r="AV8" s="7"/>
+      <c r="AW8" s="7"/>
+      <c r="AX8" s="7"/>
+      <c r="AY8" s="7"/>
+      <c r="AZ8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BA8" s="4" t="s">
+      <c r="BA8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BB8" s="4" t="s">
+      <c r="BB8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:54" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="1">
         <v>12</v>
       </c>
@@ -757,9 +757,9 @@
       <c r="AY9" s="1">
         <v>20</v>
       </c>
-      <c r="AZ9" s="5"/>
-      <c r="BA9" s="5"/>
-      <c r="BB9" s="5"/>
+      <c r="AZ9" s="7"/>
+      <c r="BA9" s="7"/>
+      <c r="BB9" s="7"/>
     </row>
     <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -1399,31 +1399,31 @@
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4">
         <v>5</v>
       </c>
-      <c r="D18" s="6"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="3">
         <v>4</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6" t="s">
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="Q18" s="3"/>

--- a/Оценки за период.xlsx
+++ b/Оценки за период.xlsx
@@ -53,19 +53,19 @@
     <t>У</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>Иностранный язык (Английский)</t>
   </si>
   <si>
-    <t>5</t>
+    <t>4</t>
   </si>
   <si>
     <t>Литературное чтение</t>
   </si>
   <si>
     <t>Математика</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>Музыка</t>
@@ -426,7 +426,9 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -457,21 +459,21 @@
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
       <c r="AO10" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP10" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
@@ -481,7 +483,9 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -512,16 +516,16 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AP11" s="3">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AQ11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -533,10 +537,14 @@
         <v>12</v>
       </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -567,20 +575,20 @@
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
       <c r="AO12" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP12" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
@@ -588,9 +596,13 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -622,10 +634,10 @@
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AP13" s="3">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AQ13" s="3"/>
     </row>
@@ -842,7 +854,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>12</v>
@@ -854,7 +866,9 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -906,7 +920,9 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -938,10 +954,10 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP19" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ19" s="3"/>
     </row>

--- a/Оценки за период.xlsx
+++ b/Оценки за период.xlsx
@@ -433,7 +433,9 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
+      <c r="P10" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
@@ -490,7 +492,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+      <c r="P11" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
@@ -516,10 +520,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AP11" s="3">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AQ11" s="3"/>
     </row>
@@ -548,7 +552,9 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="O12" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -604,10 +610,14 @@
         <v>15</v>
       </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
+      <c r="O13" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
@@ -634,10 +644,10 @@
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AP13" s="3">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AQ13" s="3"/>
     </row>
@@ -656,7 +666,9 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="M14" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -685,10 +697,10 @@
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP14" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ14" s="3"/>
     </row>
@@ -707,7 +719,9 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="M15" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -736,10 +750,10 @@
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP15" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ15" s="3"/>
     </row>
@@ -762,7 +776,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
+      <c r="O16" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -870,9 +886,13 @@
         <v>13</v>
       </c>
       <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="M18" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
+      <c r="O18" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -899,10 +919,10 @@
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AP18" s="3">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AQ18" s="3"/>
     </row>
@@ -927,7 +947,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
+      <c r="O19" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>

--- a/Оценки за период.xlsx
+++ b/Оценки за период.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Учебный год: 2025/2026</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>Литературное чтение</t>
@@ -164,7 +167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A3:AQ21"/>
+  <dimension ref="A3:AP21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -206,7 +209,6 @@
     <col min="37" max="37" width="9.140625" customWidth="1"/>
     <col min="38" max="38" width="9.140625" customWidth="1"/>
     <col min="39" max="39" width="9.140625" customWidth="1"/>
-    <col min="40" max="40" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -277,14 +279,13 @@
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
-      <c r="AN8" s="1"/>
+      <c r="AN8" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="AO8" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AQ8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -390,26 +391,23 @@
         <v>15</v>
       </c>
       <c r="AI9" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ9" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK9" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL9" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM9" s="1">
-        <v>21</v>
-      </c>
-      <c r="AN9" s="1">
         <v>22</v>
       </c>
+      <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
-      <c r="AQ9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
@@ -440,7 +438,9 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
+      <c r="U10" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
@@ -459,14 +459,13 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
-      <c r="AN10" s="3"/>
+      <c r="AN10" s="3">
+        <v>5</v>
+      </c>
       <c r="AO10" s="3">
         <v>5</v>
       </c>
-      <c r="AP10" s="3">
-        <v>5</v>
-      </c>
-      <c r="AQ10" s="3"/>
+      <c r="AP10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
@@ -497,9 +496,13 @@
       </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
+      <c r="S11" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
+      <c r="U11" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
@@ -518,18 +521,17 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
+      <c r="AN11" s="3">
+        <v>4.4</v>
+      </c>
       <c r="AO11" s="3">
-        <v>4.67</v>
-      </c>
-      <c r="AP11" s="3">
-        <v>4.6</v>
-      </c>
-      <c r="AQ11" s="3"/>
+        <v>4.25</v>
+      </c>
+      <c r="AP11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -556,13 +558,19 @@
         <v>12</v>
       </c>
       <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
+      <c r="Q12" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
+      <c r="U12" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="W12" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
@@ -579,18 +587,17 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
+      <c r="AN12" s="3">
+        <v>5</v>
+      </c>
       <c r="AO12" s="3">
         <v>5</v>
       </c>
-      <c r="AP12" s="3">
-        <v>5</v>
-      </c>
-      <c r="AQ12" s="3"/>
+      <c r="AP12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
@@ -622,9 +629,13 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
+      <c r="T13" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
+      <c r="V13" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
@@ -642,18 +653,17 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
+      <c r="AN13" s="3">
+        <v>4.5</v>
+      </c>
       <c r="AO13" s="3">
         <v>4.5</v>
       </c>
-      <c r="AP13" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="AQ13" s="3"/>
+      <c r="AP13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -673,7 +683,9 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
+      <c r="R14" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -695,18 +707,17 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
-      <c r="AN14" s="3"/>
+      <c r="AN14" s="3">
+        <v>5</v>
+      </c>
       <c r="AO14" s="3">
         <v>5</v>
       </c>
-      <c r="AP14" s="3">
-        <v>5</v>
-      </c>
-      <c r="AQ14" s="3"/>
+      <c r="AP14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -731,7 +742,9 @@
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
+      <c r="W15" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -748,18 +761,17 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
-      <c r="AN15" s="3"/>
+      <c r="AN15" s="3">
+        <v>4</v>
+      </c>
       <c r="AO15" s="3">
-        <v>5</v>
-      </c>
-      <c r="AP15" s="3">
-        <v>5</v>
-      </c>
-      <c r="AQ15" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="AP15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -803,18 +815,17 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
-      <c r="AN16" s="3"/>
+      <c r="AN16" s="3">
+        <v>0</v>
+      </c>
       <c r="AO16" s="3">
         <v>0</v>
       </c>
-      <c r="AP16" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -854,20 +865,21 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
-      <c r="AN17" s="3"/>
+      <c r="AN17" s="3">
+        <v>0</v>
+      </c>
       <c r="AO17" s="3">
         <v>0</v>
       </c>
-      <c r="AP17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="3"/>
+      <c r="AP17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
         <v>13</v>
@@ -880,7 +892,9 @@
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="I18" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
         <v>13</v>
@@ -898,7 +912,9 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
+      <c r="U18" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
@@ -917,18 +933,17 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
-      <c r="AN18" s="3"/>
+      <c r="AN18" s="3">
+        <v>4.5</v>
+      </c>
       <c r="AO18" s="3">
-        <v>4.67</v>
-      </c>
-      <c r="AP18" s="3">
-        <v>4.67</v>
-      </c>
-      <c r="AQ18" s="3"/>
+        <v>4.5</v>
+      </c>
+      <c r="AP18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -954,7 +969,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
+      <c r="T19" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -974,18 +991,17 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
-      <c r="AN19" s="3"/>
+      <c r="AN19" s="3">
+        <v>5</v>
+      </c>
       <c r="AO19" s="3">
         <v>5</v>
       </c>
-      <c r="AP19" s="3">
-        <v>5</v>
-      </c>
-      <c r="AQ19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1025,18 +1041,17 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
-      <c r="AN20" s="3"/>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
       <c r="AO20" s="3">
         <v>0</v>
       </c>
-      <c r="AP20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="3"/>
+      <c r="AP20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1078,24 +1093,23 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
-      <c r="AN21" s="3"/>
+      <c r="AN21" s="3">
+        <v>0</v>
+      </c>
       <c r="AO21" s="3">
         <v>0</v>
       </c>
-      <c r="AP21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="3"/>
+      <c r="AP21" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:Y8"/>
-    <mergeCell ref="Z8:AN8"/>
+    <mergeCell ref="Z8:AM8"/>
+    <mergeCell ref="AN8:AN9"/>
     <mergeCell ref="AO8:AO9"/>
     <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
   </mergeCells>
   <headerFooter/>
 </worksheet>

--- a/Оценки за период.xlsx
+++ b/Оценки за период.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Учебный год: 2025/2026</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Русский язык</t>
+  </si>
+  <si>
+    <t>4, 4</t>
   </si>
   <si>
     <t>Труд (технология)</t>
@@ -505,7 +508,9 @@
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
@@ -522,10 +527,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AO11" s="3">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AP11" s="3"/>
     </row>
@@ -572,7 +577,9 @@
         <v>13</v>
       </c>
       <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
+      <c r="Y12" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
@@ -636,9 +643,13 @@
       <c r="V13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="W13" s="3"/>
+      <c r="W13" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
+      <c r="Y13" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
@@ -654,10 +665,10 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="AO13" s="3">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AP13" s="3"/>
     </row>
@@ -800,7 +811,9 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
+      <c r="Y16" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
@@ -903,13 +916,17 @@
       <c r="M18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N18" s="3"/>
+      <c r="N18" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="O18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
+      <c r="R18" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3" t="s">
@@ -918,7 +935,9 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
+      <c r="Y18" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
@@ -934,16 +953,16 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
       <c r="AN18" s="3">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AO18" s="3">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="AP18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -976,7 +995,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
+      <c r="Y19" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
@@ -1001,26 +1022,38 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
+      <c r="L20" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
+      <c r="Q20" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
+      <c r="S20" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
@@ -1042,16 +1075,16 @@
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
       <c r="AN20" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO20" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
